--- a/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
+++ b/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:17:56+00:00</t>
+    <t>2026-07-29T14:24:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
+++ b/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:24:14+00:00</t>
+    <t>2026-07-29T14:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
+++ b/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:28:33+00:00</t>
+    <t>2026-07-29T15:27:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
+++ b/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T15:27:36+00:00</t>
+    <t>2026-07-29T15:42:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
+++ b/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T15:42:51+00:00</t>
+    <t>2026-07-29T15:49:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
+++ b/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T15:49:10+00:00</t>
+    <t>2026-07-29T17:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
+++ b/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:00:21+00:00</t>
+    <t>2026-07-29T17:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
+++ b/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:48:26+00:00</t>
+    <t>2026-07-29T18:33:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
+++ b/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T18:33:10+00:00</t>
+    <t>2026-07-29T18:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
+++ b/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T18:40:58+00:00</t>
+    <t>2026-07-29T18:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
+++ b/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T18:47:09+00:00</t>
+    <t>2026-07-29T18:50:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
+++ b/branches/preview/artifact-rendering-demo/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T18:50:35+00:00</t>
+    <t>2026-07-29T18:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
